--- a/experiments/results/cabp/iteration-bfs/cabp-sat-iteration-bfs.xlsx
+++ b/experiments/results/cabp/iteration-bfs/cabp-sat-iteration-bfs.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x0.5-10" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x0.75-10" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x1.25" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_cabp_x1.5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ite_cabp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ite_cabp_x0.5_has_hole" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ite_cabp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ite_cabp_x0.75_has_hole" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ite_cabp_x1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ite_cabp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ite_cabp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,71 +419,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -546,17 +541,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -609,17 +607,20 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -672,17 +673,20 @@
           <t>18</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -735,17 +739,20 @@
           <t>24</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>23</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>13.2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -798,17 +805,20 @@
           <t>24</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>23</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -861,17 +871,20 @@
           <t>25</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>24</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -924,17 +937,20 @@
           <t>25</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>24</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -987,17 +1003,20 @@
           <t>24</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>23</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>78.8</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1295</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1050,17 +1069,20 @@
           <t>40</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>133.6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1113,17 +1135,20 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>49</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>273.9</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1806740</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1172,17 +1197,20 @@
           <t>56</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>261.3</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>814</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1235,17 +1263,20 @@
           <t>56</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>256.2</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>962</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1298,17 +1329,20 @@
           <t>192</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>191</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>6120.1</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1812645</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1357,17 +1391,20 @@
           <t>192</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>191</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>6139</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>1812486</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1416,17 +1453,20 @@
           <t>208</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>207</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>4044.1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>92498</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1479,17 +1519,20 @@
           <t>182</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>181</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>5386.9</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>1809106</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1538,17 +1581,20 @@
           <t>246</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>245</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>5023</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>53865</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1601,17 +1647,20 @@
           <t>248</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>247</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>8646.5</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>489432</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1664,17 +1713,20 @@
           <t>267</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>266</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>7837.6</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>1316475</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1727,17 +1779,20 @@
           <t>230</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>229</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>9005.6</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>1811266</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1786,17 +1841,20 @@
           <t>328</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>327</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>9063.5</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>131584</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1851,15 +1909,20 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>12013.9</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>1812234</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1908,17 +1971,20 @@
           <t>342</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>341</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>9795.7</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>187245</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1971,17 +2037,20 @@
           <t>300</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>299</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>12968.9</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>328631</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1998,71 +2067,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -2097,35 +2171,38 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>12</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2160,35 +2237,38 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>15</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2223,35 +2303,38 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>17</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2286,35 +2369,38 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>23</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2349,35 +2435,38 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>23</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2412,35 +2501,38 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>70.6</t>
-        </is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>24</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2475,35 +2567,38 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>92.8</t>
-        </is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>24</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2538,35 +2633,38 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>136.3</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>23</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
+        <is>
+          <t>2348</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2601,35 +2699,38 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>197.2</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>39</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>79723</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2664,35 +2765,42 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>450.8</t>
-        </is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>47</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1808241</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>192.3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2723,35 +2831,38 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>378.4</t>
-        </is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>47134</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2786,35 +2897,38 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>431.4</t>
-        </is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>208.8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2849,35 +2963,38 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>158</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>9097.5</t>
-        </is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>191</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1812865</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>6125.3</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1813969</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2908,35 +3025,38 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>158</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>9039.3</t>
-        </is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>191</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1812835</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>6109.1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1813943</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2967,35 +3087,38 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>207</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>6485.3</t>
-        </is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>207</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>856764</t>
+          <t>3968.1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>31076</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3030,35 +3153,42 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>181</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>7768.2</t>
-        </is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>181</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1811782</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>5072</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1292460</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3089,35 +3219,38 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>247</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>7767</t>
-        </is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>245</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>110718</t>
+          <t>4664.2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
+        <is>
+          <t>27064</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3152,35 +3285,42 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>251</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>12336.8</t>
-        </is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>247</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1812682</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>8383.2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>370403</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3211,35 +3351,42 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>273</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>12098.3</t>
-        </is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>258</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1812824</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>6837.7</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>25084</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3270,35 +3417,42 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>296</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>13571.6</t>
-        </is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>224</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1812838</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>7802.9</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>68573</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3329,35 +3483,38 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>331</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>13694.6</t>
-        </is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>327</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>622165</t>
+          <t>8288.7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
+        <is>
+          <t>64254</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3392,35 +3549,42 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>337</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>18160.8</t>
-        </is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>328</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1813008</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>11256.4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>40362</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3451,35 +3615,38 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>342</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>341</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>14694.3</t>
-        </is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>341</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>390427</t>
+          <t>9843.1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
+        <is>
+          <t>85911</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3514,35 +3681,42 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>357</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>19290.4</t>
-        </is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>299</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1813307</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>11419.4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>128067</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3555,71 +3729,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -3654,35 +3833,38 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>17</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3717,35 +3899,38 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>23</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3780,35 +3965,38 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>61.7</t>
-        </is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>26</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3843,35 +4031,38 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>101.4</t>
-        </is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>35</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3906,35 +4097,38 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>81.6</t>
-        </is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>35</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3969,35 +4163,38 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>110.7</t>
-        </is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>34</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4032,35 +4229,38 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>115.4</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>39</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4095,35 +4295,38 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>217.8</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>39</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4158,35 +4361,38 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>325.7</t>
-        </is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>197.2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
+        <is>
+          <t>79723</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4221,39 +4427,38 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>382.4</t>
-        </is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>74</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>450.8</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1808241</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4284,35 +4489,38 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>531.5</t>
-        </is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>83</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>378.4</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
+        <is>
+          <t>47134</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4347,35 +4555,38 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>538.8</t>
-        </is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>83</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>431.4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4410,35 +4621,38 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>315</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>12954.9</t>
-        </is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>296</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1813104</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>9097.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1812865</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4469,35 +4683,38 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>315</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>13015.9</t>
-        </is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>296</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1812609</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>9039.3</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1812835</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4528,35 +4745,38 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>318</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>311</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>8200.8</t>
-        </is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>311</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>61567</t>
+          <t>6485.3</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>856764</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4591,35 +4811,38 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>333</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>10192.7</t>
-        </is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>275</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1812527</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>7768.2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1811782</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4650,35 +4873,38 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>370</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>368</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>10017.3</t>
-        </is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>368</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>70010</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
+        <is>
+          <t>110718</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4713,39 +4939,38 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>377</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>15955.6</t>
-        </is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>375</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>866373</t>
+          <t>12336.8</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1812682</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4776,39 +5001,38 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>409</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>14638.3</t>
-        </is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>402</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>41579</t>
+          <t>12098.3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1812824</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4839,39 +5063,38 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>444</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>336</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>16895.5</t>
-        </is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>344</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>161614</t>
+          <t>13571.6</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1812838</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4902,35 +5125,38 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>496</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>491</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>18443.5</t>
-        </is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>491</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>77614</t>
+          <t>13694.6</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
+        <is>
+          <t>622165</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4965,39 +5191,40 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>506</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>492</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20568.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>45401</t>
+          <t>18160.8</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1813008</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5028,35 +5255,38 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>513</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>509</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>19565.1</t>
-        </is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>509</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>131643</t>
+          <t>14694.3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
+        <is>
+          <t>390427</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5091,39 +5321,38 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>449</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>24017.3</t>
-        </is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>457</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>184640</t>
+          <t>19290.4</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1813307</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5136,71 +5365,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -5235,35 +5469,38 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>16</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5298,35 +5535,38 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>68.9</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>23</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5361,35 +5601,38 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>85.1</t>
-        </is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>26</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5424,35 +5667,38 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>35</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5487,35 +5733,38 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>35</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>83</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5550,35 +5799,38 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>128.2</t>
-        </is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>34</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5613,35 +5865,38 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>124.6</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>39</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5676,35 +5931,38 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>227.2</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>39</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
+        <is>
+          <t>5019</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5739,35 +5997,38 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>414.3</t>
-        </is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>201.4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5802,35 +6063,38 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>475.8</t>
-        </is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>71</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>286.7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5865,35 +6129,38 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>663.7</t>
-        </is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>81</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>384.2</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5928,35 +6195,38 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>665.6</t>
-        </is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>83</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>297.4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
+        <is>
+          <t>1798</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5991,35 +6261,38 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>315</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>15876.7</t>
-        </is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>287</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1813657</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>9408.7</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1813860</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6050,35 +6323,38 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>315</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>16162.5</t>
-        </is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>287</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1812807</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>9527.9</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1813855</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6109,35 +6385,38 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>318</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>311</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>10590.2</t>
-        </is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>311</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>6218.8</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>50071</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6172,35 +6451,42 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>333</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>12671.2</t>
-        </is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>274</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1813103</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>7699</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1779394</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6231,35 +6517,38 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>370</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>368</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>12379.5</t>
-        </is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>368</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>7310.8</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
+        <is>
+          <t>56164</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6294,35 +6583,38 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>377</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>19462.9</t>
-        </is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>367</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1039251</t>
+          <t>11660.3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
+        <is>
+          <t>504422</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6357,35 +6649,38 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>194</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>409</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>386</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>19657.9</t>
-        </is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>386</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>60101</t>
+          <t>11183</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
+        <is>
+          <t>46734</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6420,35 +6715,38 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>444</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>336</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>21397.3</t>
-        </is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>336</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>146368</t>
+          <t>12292.7</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
+        <is>
+          <t>107989</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6483,35 +6781,38 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>496</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>491</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>23763.1</t>
-        </is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>491</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>104911</t>
+          <t>13713.2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
+        <is>
+          <t>65826</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6546,35 +6847,38 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>506</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>492</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>820</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>27432.7</t>
-        </is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>492</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>79453</t>
+          <t>16417.8</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
+        <is>
+          <t>71326</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6609,35 +6913,38 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>513</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>509</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>852</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>24594.2</t>
-        </is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>509</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>150229</t>
+          <t>15007.8</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
+        <is>
+          <t>102342</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6672,35 +6979,42 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>536</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>449</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>30071.5</t>
-        </is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>449</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>108125</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>16705.3</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>194969</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6713,71 +7027,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -6812,35 +7131,38 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6875,35 +7197,38 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>31</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6938,35 +7263,38 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>38</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7001,35 +7329,38 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>152.8</t>
-        </is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>47</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7064,35 +7395,38 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>134.2</t>
-        </is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>47</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7127,35 +7461,38 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>157.2</t>
-        </is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>49</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>110.7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7190,35 +7527,38 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>184.1</t>
-        </is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>54</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>115.4</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7253,35 +7593,38 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>305.7</t>
-        </is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>217.8</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
+        <is>
+          <t>6891</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7316,35 +7659,38 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>509.6</t>
-        </is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>83</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>325.7</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7379,35 +7725,38 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>564.9</t>
-        </is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>95</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>382.4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7442,35 +7791,38 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>117</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>799.4</t>
-        </is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>110</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>531.5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
+        <is>
+          <t>2077</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7505,35 +7857,38 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>810.1</t>
-        </is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>115</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>538.8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7568,35 +7923,38 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>420</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>19188.8</t>
-        </is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>395</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1813460</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>12954.9</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1813104</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7627,35 +7985,38 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>34</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>420</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>19315.4</t>
-        </is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>395</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1812904</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>13015.9</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1812609</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7686,35 +8047,38 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>425</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>419</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>12785.1</t>
-        </is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>419</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>105529</t>
+          <t>8200.8</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>61567</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7749,35 +8113,38 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>445</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>364</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>15169.7</t>
-        </is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>367</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1812835</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>10192.7</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1812527</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7808,35 +8175,38 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>494</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>491</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>15084.7</t>
-        </is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>491</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>74575</t>
+          <t>10017.3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
+        <is>
+          <t>70010</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7871,35 +8241,38 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>495</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>24390.9</t>
-        </is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>495</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1382776</t>
+          <t>15955.6</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
+        <is>
+          <t>866373</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7934,35 +8307,38 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>546</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>515</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>23769</t>
-        </is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>515</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>74750</t>
+          <t>14638.3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
+        <is>
+          <t>41579</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7997,35 +8373,38 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>592</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>451</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>25319.9</t>
-        </is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>451</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>184995</t>
+          <t>16895.5</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
+        <is>
+          <t>161614</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -8060,35 +8439,38 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>662</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>659</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>988</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>29150.9</t>
-        </is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>659</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>148229</t>
+          <t>18443.5</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
+        <is>
+          <t>77614</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -8123,35 +8505,42 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>675</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>655</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>30190.5</t>
-        </is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>655</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>67166</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>20568.3</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>45401</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8182,35 +8571,42 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>685</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>683</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>30084.3</t>
-        </is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>683</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>91468</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>19565.1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>131643</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8241,6 +8637,3314 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>605</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>24017.3</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>184640</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Memory limit (MB)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Real time limit (s)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Worker count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Highest label UNSAT</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Lowest label SAT</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Memory consumed (MB)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Time consumed (ms)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Optimal found</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-pores_1.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A-pores_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-ibm32.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B-ibm32</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>39</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>68.9</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.txt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>47</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>85.1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-curtis54.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F-curtis54</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>128.2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G-will57.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G-will57</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>64</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>124.6</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H-impcol_b</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>63</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>227.2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>8700</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-ash85.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I-ash85</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>103</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>414.3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1816</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J-nos4.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J-nos4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>119</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>475.8</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K-dwt__234</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>136</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>663.7</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2827</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>143</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>665.6</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2873</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>494</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>15876.7</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1813657</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>494</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>16162.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1812807</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O-impcol_d</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>523</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10590.2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>76160</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-can__445.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-can__445</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>458</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>12671.2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1813103</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Q-494_bus</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>614</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>12379.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>57941</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R-dwt__503</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>615</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>19462.9</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1039251</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S-sherman4.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S-sherman4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>643</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>19657.9</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>60101</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T-dwt__592</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>563</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>21397.3</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>146368</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U-662_bus.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U-662_bus</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>823</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>23763.1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>104911</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V-nos6.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-nos6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>819</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>27432.7</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>79453</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W-685_bus.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W-685_bus</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>851</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>24594.2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>150229</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>X-can__715.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>X-can__715</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>797</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>30071.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>108125</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Memory limit (MB)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Real time limit (s)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Worker count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Highest label UNSAT</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Lowest label SAT</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Memory consumed (MB)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Time consumed (ms)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Optimal found</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-pores_1.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A-pores_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>61.2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-ibm32.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B-ibm32</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>47</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.txt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>56</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>71</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>152.8</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>71</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>134.2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-curtis54.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F-curtis54</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>74</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>157.2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G-will57.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G-will57</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>79</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>184.1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H-impcol_b</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>79</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>305.7</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>16395</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-ash85.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I-ash85</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>123</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>509.6</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J-nos4.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J-nos4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>143</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>564.9</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K-dwt__234</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>165</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>799.4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>171</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>810.1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4781</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>593</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>19188.8</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1813460</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>593</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>19315.4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1812904</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O-impcol_d</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>627</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>12785.1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>105529</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-can__445.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-can__445</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>549</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>15169.7</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1812835</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Q-494_bus</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>737</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>15084.7</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>74575</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R-dwt__503</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>743</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>24390.9</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1382776</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S-sherman4.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S-sherman4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>773</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>23769</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>74750</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T-dwt__592</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>675</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>25319.9</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>184995</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U-662_bus.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U-662_bus</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>987</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>29150.9</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>148229</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V-nos6.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-nos6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>30190.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>67166</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W-685_bus.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W-685_bus</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>30084.3</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>91468</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>X-can__715.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>X-can__715</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
@@ -8259,17 +11963,20 @@
           <t>958</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>957</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>30319.4</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>154943</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
